--- a/DAY 58/tasks.xlsx
+++ b/DAY 58/tasks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,23 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>2026-04-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prepare Assignment</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1 PM</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
         </is>
       </c>
     </row>
